--- a/marketing_forms/008_marketing_agents_registration_form--marketing_forms.xlsx
+++ b/marketing_forms/008_marketing_agents_registration_form--marketing_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>company_name</t>
+          <t>Company Name</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -571,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>company_email</t>
+          <t>Company Email</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -594,7 +594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>contact_number</t>
+          <t>Contact Number</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -617,7 +617,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>address_1</t>
+          <t>Address 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -640,7 +640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>address_2</t>
+          <t>Address 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -663,7 +663,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>city</t>
+          <t>City</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -686,7 +686,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>state</t>
+          <t>State</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -709,7 +709,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>zip</t>
+          <t>Zip</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -732,7 +732,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>website</t>
+          <t>Website</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>contact_name</t>
+          <t>work_number</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>contact_name</t>
+          <t>Work Number</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>contact_number</t>
+          <t>job_title</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>contact_number</t>
+          <t>Job Title</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,17 +791,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>role</t>
+          <t>company_description</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>role</t>
+          <t>Company Description</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -814,17 +814,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>job_title</t>
+          <t>industry</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>job_title</t>
+          <t>Industry</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>company_description</t>
+          <t>services_offered</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>company_description</t>
+          <t>Services Offered</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -860,17 +860,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>industry</t>
+          <t>company_address</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>industry</t>
+          <t>Company Address</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>services_offered</t>
+          <t>company_phone_number</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>services_offered</t>
+          <t>Company Phone Number</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>company_logo</t>
+          <t>job_description</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>company_logo</t>
+          <t>Job Description</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>resume</t>
+          <t>additional_info</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>resume</t>
+          <t>Additional Information</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -962,7 +962,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>agreement_terms</t>
+          <t>Agreement Terms</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>submit</t>
+          <t>job_agreement_confirmation</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>submit</t>
+          <t>Job Agreement Confirmation</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>agreement_terms</t>
+          <t>confirm_agreement</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>agreement_terms</t>
+          <t>Confirm Agreement</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1026,62 +1026,16 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>confirm_agreement</t>
+          <t>submit</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>confirm_agreement</t>
+          <t>Submit</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>confirm</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>confirm</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>submit</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>submit</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,7 +1052,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1160,7 +1114,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>role_choices</t>
+          <t>industry_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1177,7 +1131,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>role_choices</t>
+          <t>industry_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1186,40 +1140,6 @@
         </is>
       </c>
       <c r="C5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>industry_choices</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>industry_choices</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
